--- a/public/plantilla-com-resumen.xlsx
+++ b/public/plantilla-com-resumen.xlsx
@@ -16,8 +16,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -195,7 +195,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -293,6 +293,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6FAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -598,7 +603,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
@@ -732,7 +737,7 @@
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -741,7 +746,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -966,7 +971,7 @@
     <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -978,7 +983,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1100,7 +1105,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1109,6 +1114,18 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11400,32 +11417,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2252203</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>177646</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>2252203</colOff>
+      <row>7</row>
+      <rowOff>177646</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3564000" cy="1692000"/>
@@ -11436,11 +11453,11 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11742,6 +11759,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I12"/>
@@ -11756,6 +11774,9 @@
     <col width="18" customWidth="1" style="67" min="7" max="7"/>
     <col width="9" customWidth="1" style="67" min="8" max="8"/>
     <col width="16" customWidth="1" style="67" min="9" max="9"/>
+    <col width="8.88671875" customWidth="1" style="67" min="10" max="10"/>
+    <col width="8.88671875" customWidth="1" style="67" min="11" max="11"/>
+    <col width="8.88671875" customWidth="1" style="67" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="67">
@@ -11797,7 +11818,7 @@
         </is>
       </c>
       <c r="F5" s="29" t="n"/>
-      <c r="G5" s="93" t="inlineStr">
+      <c r="G5" s="187" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
@@ -11816,7 +11837,7 @@
         </is>
       </c>
       <c r="F6" s="29" t="n"/>
-      <c r="G6" s="93" t="inlineStr">
+      <c r="G6" s="187" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
@@ -11830,7 +11851,7 @@
       <c r="D7" s="68" t="n"/>
       <c r="E7" s="68" t="n"/>
       <c r="F7" s="68" t="n"/>
-      <c r="G7" s="93" t="inlineStr">
+      <c r="G7" s="187" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
@@ -11846,7 +11867,7 @@
       <c r="D8" s="68" t="n"/>
       <c r="E8" s="68" t="n"/>
       <c r="F8" s="68" t="n"/>
-      <c r="G8" s="95" t="inlineStr">
+      <c r="G8" s="188" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
@@ -11859,7 +11880,7 @@
       <c r="I8" s="112" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="67">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="189" t="inlineStr">
         <is>
           <t>Resumen mensual de compras de la obra: lo pedido, comprado, recibido y pendiente, frente al presupuesto y por proveedor</t>
         </is>
@@ -11889,7 +11910,7 @@
       <c r="I10" s="32" t="n"/>
     </row>
     <row r="11" ht="22.05" customHeight="1" s="67">
-      <c r="A11" s="81" t="inlineStr">
+      <c r="A11" s="190" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
@@ -11897,13 +11918,13 @@
       <c r="B11" s="32" t="n"/>
       <c r="C11" s="161" t="n"/>
       <c r="D11" s="163" t="n"/>
-      <c r="E11" s="81" t="inlineStr">
+      <c r="E11" s="190" t="inlineStr">
         <is>
           <t>Contrato N°</t>
         </is>
       </c>
       <c r="F11" s="164" t="n"/>
-      <c r="G11" s="81" t="inlineStr">
+      <c r="G11" s="190" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
@@ -11912,7 +11933,7 @@
       <c r="I11" s="165" t="n"/>
     </row>
     <row r="12" ht="22.05" customHeight="1" s="67">
-      <c r="A12" s="81" t="inlineStr">
+      <c r="A12" s="190" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
@@ -11920,13 +11941,13 @@
       <c r="B12" s="32" t="n"/>
       <c r="C12" s="161" t="n"/>
       <c r="D12" s="163" t="n"/>
-      <c r="E12" s="81" t="inlineStr">
+      <c r="E12" s="190" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="F12" s="164" t="n"/>
-      <c r="G12" s="81" t="inlineStr">
+      <c r="G12" s="190" t="inlineStr">
         <is>
           <t>Fecha de corte</t>
         </is>
